--- a/data/dividends_info_20260624.xlsx
+++ b/data/dividends_info_20260624.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>64.27999877929688</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1400124482096085</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J2" t="n">
         <v>264</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.80000305175781</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>1.080246862705991</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="J3" t="n">
         <v>243</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.180000305175781</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6535947495140209</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J4" t="n">
         <v>173</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>64.27999877929688</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1400124482096085</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J6" t="n">
         <v>173</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.019999980926514</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>3.811881224111814</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J7" t="n">
         <v>152</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.2450008392334</v>
+        <v>20.79500007629395</v>
       </c>
       <c r="I8" t="n">
-        <v>1.270887217388986</v>
+        <v>1.298389031062312</v>
       </c>
       <c r="J8" t="n">
         <v>152</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.900000095367432</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I9" t="n">
-        <v>3.389830453681454</v>
+        <v>3.384094842025701</v>
       </c>
       <c r="J9" t="n">
         <v>145</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.96999979019165</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J13" t="n">
         <v>96</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.2450008392334</v>
+        <v>20.79500007629395</v>
       </c>
       <c r="I14" t="n">
-        <v>1.270887217388986</v>
+        <v>1.298389031062312</v>
       </c>
       <c r="J14" t="n">
         <v>89</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>64.27999877929688</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1400124482096085</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J15" t="n">
         <v>89</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.019999980926514</v>
+        <v>6.039999961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>4.983388720108072</v>
+        <v>4.966887448588033</v>
       </c>
       <c r="J16" t="n">
         <v>82</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.96999979019165</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J18" t="n">
         <v>40</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.559999942779541</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I19" t="n">
-        <v>4.496402923972346</v>
+        <v>4.587156123840477</v>
       </c>
       <c r="J19" t="n">
         <v>33</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.070000171661377</v>
+        <v>4.099999904632568</v>
       </c>
       <c r="I20" t="n">
-        <v>3.439803294722022</v>
+        <v>3.414634225767048</v>
       </c>
       <c r="J20" t="n">
         <v>26</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.854999542236328</v>
+        <v>9.866999626159668</v>
       </c>
       <c r="I21" t="n">
-        <v>2.638254815595861</v>
+        <v>2.635046213143463</v>
       </c>
       <c r="J21" t="n">
         <v>26</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15.5</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="I22" t="n">
-        <v>3.870967741935484</v>
+        <v>3.886010468305368</v>
       </c>
       <c r="J22" t="n">
         <v>26</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.380000114440918</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I23" t="n">
-        <v>6.508875519265772</v>
+        <v>6.413994044262304</v>
       </c>
       <c r="J23" t="n">
         <v>26</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.320000171661377</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I25" t="n">
-        <v>1.582278438035428</v>
+        <v>1.550387642746198</v>
       </c>
       <c r="J25" t="n">
         <v>26</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.75</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I27" t="n">
-        <v>2.08695652173913</v>
+        <v>2.090592417856904</v>
       </c>
       <c r="J27" t="n">
         <v>19</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.34999847412109</v>
+        <v>34.84999847412109</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4366812421054642</v>
+        <v>0.4304160877119894</v>
       </c>
       <c r="J32" t="n">
         <v>12</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.60000038146973</v>
+        <v>21.57999992370605</v>
       </c>
       <c r="I34" t="n">
-        <v>1.157407386966857</v>
+        <v>1.158480078238416</v>
       </c>
       <c r="J34" t="n">
         <v>-2</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29</v>
+        <v>29.14999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6689536965758348</v>
       </c>
       <c r="J35" t="n">
         <v>-2</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.809999942779541</v>
+        <v>1.799999952316284</v>
       </c>
       <c r="I36" t="n">
-        <v>1.823204477527402</v>
+        <v>1.833333381900082</v>
       </c>
       <c r="J36" t="n">
         <v>-2</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.125</v>
+        <v>5.195000171661377</v>
       </c>
       <c r="I37" t="n">
-        <v>5.658536585365853</v>
+        <v>5.582290479641257</v>
       </c>
       <c r="J37" t="n">
         <v>-2</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.618000030517578</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="I38" t="n">
-        <v>4.422332743239667</v>
+        <v>4.383561529301643</v>
       </c>
       <c r="J38" t="n">
         <v>-2</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.490000009536743</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="I39" t="n">
-        <v>5.566265038922072</v>
+        <v>5.611335967392061</v>
       </c>
       <c r="J39" t="n">
         <v>-2</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>47.94499969482422</v>
+        <v>48.02999877929688</v>
       </c>
       <c r="I40" t="n">
-        <v>1.314005639816513</v>
+        <v>1.311680233211996</v>
       </c>
       <c r="J40" t="n">
         <v>-2</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.054999828338623</v>
+        <v>6.224999904632568</v>
       </c>
       <c r="I41" t="n">
-        <v>2.312138793873647</v>
+        <v>2.248996018390518</v>
       </c>
       <c r="J41" t="n">
         <v>-2</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16.95000076293945</v>
+        <v>16.29999923706055</v>
       </c>
       <c r="I42" t="n">
-        <v>4.601769704373353</v>
+        <v>4.78527629759976</v>
       </c>
       <c r="J42" t="n">
         <v>-2</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.36000061035156</v>
+        <v>28.22999954223633</v>
       </c>
       <c r="I43" t="n">
-        <v>2.997179061024932</v>
+        <v>3.010981274471054</v>
       </c>
       <c r="J43" t="n">
         <v>-2</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>64.27999877929688</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1400124482096085</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J44" t="n">
         <v>-2</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.222000122070312</v>
+        <v>6.288000106811523</v>
       </c>
       <c r="I46" t="n">
-        <v>2.91385400904933</v>
+        <v>2.883269671124932</v>
       </c>
       <c r="J46" t="n">
         <v>-2</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.739999771118164</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I47" t="n">
-        <v>2.974828453190412</v>
+        <v>2.954545390507408</v>
       </c>
       <c r="J47" t="n">
         <v>-2</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.10999965667725</v>
+        <v>10.16499996185303</v>
       </c>
       <c r="I48" t="n">
-        <v>2.739861616286532</v>
+        <v>2.725036901520109</v>
       </c>
       <c r="J48" t="n">
         <v>-2</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.014999985694885</v>
+        <v>1.009999990463257</v>
       </c>
       <c r="I49" t="n">
-        <v>1.330049279829072</v>
+        <v>1.336633675987259</v>
       </c>
       <c r="J49" t="n">
         <v>-9</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.956000089645386</v>
+        <v>2.937999963760376</v>
       </c>
       <c r="I50" t="n">
-        <v>3.721244812722454</v>
+        <v>3.744043613234423</v>
       </c>
       <c r="J50" t="n">
         <v>-9</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.580000042915344</v>
+        <v>1.629999995231628</v>
       </c>
       <c r="I51" t="n">
-        <v>1.518987300514011</v>
+        <v>1.47239264234412</v>
       </c>
       <c r="J51" t="n">
         <v>-9</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.990000009536743</v>
+        <v>2.984999895095825</v>
       </c>
       <c r="I52" t="n">
-        <v>5.351170551494067</v>
+        <v>5.360134191725446</v>
       </c>
       <c r="J52" t="n">
         <v>-16</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8650000095367432</v>
+        <v>0.8550000190734863</v>
       </c>
       <c r="I53" t="n">
-        <v>2.890173378540068</v>
+        <v>2.923976542958566</v>
       </c>
       <c r="J53" t="n">
         <v>-16</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.35000038146973</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>4.058500857470011</v>
+        <v>4.043715734604362</v>
       </c>
       <c r="J54" t="n">
         <v>-20</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.878000020980835</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="I55" t="n">
-        <v>3.416856410377562</v>
+        <v>3.370786571033133</v>
       </c>
       <c r="J55" t="n">
         <v>-23</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.414999961853027</v>
+        <v>2.454999923706055</v>
       </c>
       <c r="I59" t="n">
-        <v>7.453416266801352</v>
+        <v>7.331975787937011</v>
       </c>
       <c r="J59" t="n">
         <v>-30</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.59000015258789</v>
+        <v>16.77000045776367</v>
       </c>
       <c r="I61" t="n">
-        <v>1.506931872818592</v>
+        <v>1.490757264018216</v>
       </c>
       <c r="J61" t="n">
         <v>-30</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.930000066757202</v>
+        <v>3.920000076293945</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7633587656591105</v>
+        <v>0.7653061075540248</v>
       </c>
       <c r="J62" t="n">
         <v>-30</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.199999809265137</v>
+        <v>4.25</v>
       </c>
       <c r="I63" t="n">
-        <v>3.571428733618088</v>
+        <v>3.529411764705882</v>
       </c>
       <c r="J63" t="n">
         <v>-30</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.55000019073486</v>
+        <v>12.5</v>
       </c>
       <c r="I64" t="n">
-        <v>4.621513873985353</v>
+        <v>4.64</v>
       </c>
       <c r="J64" t="n">
         <v>-30</v>
@@ -5221,95 +5221,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>